--- a/Excel_Assignment.xlsx
+++ b/Excel_Assignment.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6743546b90761a27/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6743546B90761A27/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{100F5ECE-D831-4768-8F83-896B696FD188}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{3CD22226-73F7-4C64-808A-5E3A4C1DDBFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B14752BC-B517-45BE-8084-DFE5E55461FA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9495" xr2:uid="{7F818628-619B-4414-AA02-418BD3068651}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Task_1" sheetId="1" r:id="rId1"/>
+    <sheet name="Task_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Task_3" sheetId="3" r:id="rId3"/>
+    <sheet name="Task_4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="123">
   <si>
     <t>Emp_ID</t>
   </si>
@@ -320,12 +323,828 @@
   <si>
     <t>Attendance %</t>
   </si>
+  <si>
+    <t>Roll No</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>12A</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>Computer</t>
+  </si>
+  <si>
+    <t>Attendance%</t>
+  </si>
+  <si>
+    <t>Total Marks</t>
+  </si>
+  <si>
+    <t>Percentage%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Calculate the total marks obtained by each student in all four subjects. Then calculate the 
+percentage assuming the maximum marks are 400. Use suitable Excel formulas.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Q2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The school wants to award scholarships to deserving students. A student will receive a 
+scholarship if: 
+● Percentage is greater than 85% 
+● AND attendance is above 90% 
+● OR Computer marks are above 95. 
+Use IF, AND, and OR formulas to display “Scholarship Approved” or “Not Approved”.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Scholarship</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q3.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create a grading system using nested IF statements: 
+● Percentage ≥ 90 → Grade A+ 
+● Percentage ≥ 75 → Grade A 
+● Percentage ≥ 60 → Grade B 
+● Percentage ≥ 40 → Grade C 
+● Below 40 → Fail</t>
+    </r>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The principal wants to know the average marks in Maths for students who scored more than 70 
+marks in Maths. Use AVERAGEIF formula.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The administration department wants to calculate the total English marks of students belonging 
+to class 12A only. Use SUMIF formula.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The school wants to identify weak students. If a student has scored below 50 in any one 
+subject, the result should display “Needs Improvement”; otherwise display “Satisfactory”. Use 
+OR function with IF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Count the number of students whose attendance percentage is greater than 90 because they 
+are eligible for the “Best Attendance Award”. Use COUNTIF. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q8. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Create a formula to identify “Academic Excellence” students. A student should receive this title 
+if: 
+● English, Maths, Science, and Computer marks are all above 85 
+● AND attendance is above 90%. 
+Use AND with IF.</t>
+    </r>
+  </si>
+  <si>
+    <t>Academc Excellence</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>PenDrive</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Notebook</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Stationery</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Stock Available</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The sales department wants to automatically retrieve the product name and product price 
+whenever a Product ID is entered into a separate cell. Use VLOOKUP formula to fetch both 
+details from the table. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The inventory manager wants to identify products that require urgent restocking. If stock 
+available is less than 20, the result should display “Restock Immediately”; otherwise display 
+“Stock Sufficient”. Use IF formula.</t>
+    </r>
+  </si>
+  <si>
+    <t>Stock Status</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Calculate the total stock available for all products belonging to the Electronics category using 
+SUMIF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q4.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The company wants to know how many products currently have stock greater than 50 units. 
+Use COUNTIF formula.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Calculate the average price of products whose price is greater than ₹1,000 using AVERAGEIF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The management wants to identify fast-selling products. A product should be marked as “Fast 
+Moving” if: 
+● Stock is less than 30 
+● AND price is greater than ₹2,000 
+● OR category is Electronics. 
+Use IF, AND, and OR formulas.</t>
+    </r>
+  </si>
+  <si>
+    <t>Selling Status</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.  Create a horizontal sales table and use HLOOKUP formula to retrieve monthly sales figures for a 
+selected category.</t>
+    </r>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Retrieve March sales using HLOOKUP.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q8. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The store manager wants to classify products according to pricing: 
+● Above ₹7,000 → “Premium Product” 
+● ₹2,000 to ₹7,000 → “Standard Product” 
+● Below ₹2,000 → “Budget Product” 
+Use nested IF statements to generate the classification automatically.</t>
+    </r>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>E301</t>
+  </si>
+  <si>
+    <t>E302</t>
+  </si>
+  <si>
+    <t>E303</t>
+  </si>
+  <si>
+    <t>E304</t>
+  </si>
+  <si>
+    <t>E305</t>
+  </si>
+  <si>
+    <t>E306</t>
+  </si>
+  <si>
+    <t>E307</t>
+  </si>
+  <si>
+    <t>E308</t>
+  </si>
+  <si>
+    <t>Emp_Name</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The company wants to identify employees eligible for an international business trip. An 
+employee will qualify only if: 
+● Sales are greater than ₹1,00,000 AND attendance is greater than 95% 
+● OR the employee belongs to the IT department AND has more than 7 years of 
+experience. 
+Create a formula using IF, AND, and OR to display “Eligible for Trip” or “Not Eligible”.</t>
+    </r>
+  </si>
+  <si>
+    <t>International_Business_Trip</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.  The HR department wants to approve leadership promotions only for employees who satisfy the 
+following conditions: 
+● Salary greater than ₹70,000 AND performance rating is “Excellent” AND attendance 
+above 90% 
+● OR sales are greater than ₹1,30,000 regardless of department. 
+Use a combination of IF, AND, and OR formulas to display “Promotion Approved” or “Promotion 
+Rejected”.</t>
+    </r>
+  </si>
+  <si>
+    <t>Leadership Promotions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The company wants to identify employees who should receive a “Critical Employee Retention 
+Bonus”. The conditions are: 
+● Experience greater than 5 years AND salary below ₹75,000 
+● OR sales above ₹1,10,000 AND rating is “Excellent”. 
+Write a formula using IF, AND, and OR.</t>
+    </r>
+  </si>
+  <si>
+    <t>Critical Employee Retention Bonus</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q4.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The finance department wants to mark employees as “High Risk Employees” if: 
+● Attendance is below 90% AND sales are below ₹70,000 
+● OR rating is “Average” 
+● OR experience is less than 3 years. 
+Use advanced logical formulas to generate the required result.</t>
+    </r>
+  </si>
+  <si>
+    <t>High Risk Employee</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The management wants to shortlist employees for executive training. An employee should be 
+selected only if: 
+● Department is IT AND attendance above 95% AND sales above ₹90,000 
+● OR department is Sales AND sales above ₹1,20,000 AND rating is “Excellent”. 
+Use nested AND and OR formulas with IF.</t>
+    </r>
+  </si>
+  <si>
+    <t>Executive Training</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The company wants to provide a special “Loyalty Appreciation Award” to employees who satisfy 
+any one of the following conditions: 
+● Experience greater than 8 years AND attendance greater than 95% 
+● OR sales above ₹1,00,000 AND salary less than ₹80,000 
+● OR rating is “Excellent” AND department is IT. 
+Create a hard-level logical formula using multiple AND and OR conditions. </t>
+    </r>
+  </si>
+  <si>
+    <t>Loyalty Appreciation Award</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Q7. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The HR manager wants to identify employees who require performance counseling. An 
+employee should be marked for counseling if: 
+● Attendance below 90% AND sales below ₹80,000 
+● OR rating is “Average” 
+● OR salary below ₹50,000 AND experience below 4 years. 
+Use IF, AND, and OR formulas.</t>
+    </r>
+  </si>
+  <si>
+    <t>Performance Counseling</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q8.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  The company wants to identify employees who qualify for the “Elite Performer Club”. The 
+eligibility criteria are: 
+● Sales greater than ₹1,00,000 AND attendance above 95% AND rating is “Excellent” 
+● OR experience greater than 8 years AND salary greater than ₹80,000.</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Performer Club</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +1165,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -372,12 +1199,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -386,21 +1226,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,7 +1564,10 @@
   <dimension ref="A1:V69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -730,492 +1578,492 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>101</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
         <v>55000</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="1">
         <v>85000</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="1">
         <v>92</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="str">
+      <c r="H2" s="1" t="str">
         <f>IF(OR(AND(E2&gt;80000,F2&gt;90),G2="Excellent"),"Bonus Eligible","Not Eligible")</f>
         <v>Bonus Eligible</v>
       </c>
-      <c r="I2" s="3" t="str">
+      <c r="I2" s="1" t="str">
         <f>IF(D2&gt;65000,"High Income Group",IF(AND(D2&gt;50000,D2&lt;65000),"Medium Income Group","Basic Income Group"))</f>
         <v>Medium Income Group</v>
       </c>
-      <c r="J2" s="3" t="str">
+      <c r="J2" s="1" t="str">
         <f>IF(OR(AND(D2&gt;60000,E2&gt;90000),G2="Excellent",F2&gt;95),"Top Performer","Average Performer")</f>
         <v>Top Performer</v>
       </c>
-      <c r="K2" s="3" t="str">
+      <c r="K2" s="1" t="str">
         <f>IF(E2&gt;100000,"Outstanding",IF(AND(E2&gt;75000,E2&lt;100000),"Very Good",IF(AND(E2&gt;50000,E2&lt;75000),"Good","Needs Improvement")))</f>
         <v>Very Good</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>102</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="1">
         <v>42000</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>30000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="1">
         <v>88</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H9" si="0">IF(OR(AND(E3&gt;80000,F3&gt;90),G3="Excellent"),"Bonus Eligible","Not Eligible")</f>
         <v>Not Eligible</v>
       </c>
-      <c r="I3" s="3" t="str">
+      <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I9" si="1">IF(D3&gt;65000,"High Income Group",IF(AND(D3&gt;50000,D3&lt;65000),"Medium Income Group","Basic Income Group"))</f>
         <v>Basic Income Group</v>
       </c>
-      <c r="J3" s="3" t="str">
+      <c r="J3" s="1" t="str">
         <f t="shared" ref="J3:J9" si="2">IF(OR(AND(D3&gt;60000,E3&gt;90000),G3="Excellent",F3&gt;95),"Top Performer","Average Performer")</f>
         <v>Average Performer</v>
       </c>
-      <c r="K3" s="3" t="str">
+      <c r="K3" s="1" t="str">
         <f t="shared" ref="K3:K9" si="3">IF(E3&gt;100000,"Outstanding",IF(AND(E3&gt;75000,E3&lt;100000),"Very Good",IF(AND(E3&gt;50000,E3&lt;75000),"Good","Needs Improvement")))</f>
         <v>Needs Improvement</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>103</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>65000</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>95000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <v>96</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="3" t="str">
+      <c r="H4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Bonus Eligible</v>
       </c>
-      <c r="I4" s="3" t="str">
+      <c r="I4" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Basic Income Group</v>
       </c>
-      <c r="J4" s="3" t="str">
+      <c r="J4" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Top Performer</v>
       </c>
-      <c r="K4" s="3" t="str">
+      <c r="K4" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Very Good</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>104</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>48000</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>72000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="1">
         <v>85</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="3" t="str">
+      <c r="H5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Not Eligible</v>
       </c>
-      <c r="I5" s="3" t="str">
+      <c r="I5" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Basic Income Group</v>
       </c>
-      <c r="J5" s="3" t="str">
+      <c r="J5" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Average Performer</v>
       </c>
-      <c r="K5" s="3" t="str">
+      <c r="K5" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>70000</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>105000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <v>98</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="3" t="str">
+      <c r="H6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Bonus Eligible</v>
       </c>
-      <c r="I6" s="3" t="str">
+      <c r="I6" s="1" t="str">
         <f t="shared" si="1"/>
         <v>High Income Group</v>
       </c>
-      <c r="J6" s="3" t="str">
+      <c r="J6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Top Performer</v>
       </c>
-      <c r="K6" s="3" t="str">
+      <c r="K6" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Outstanding</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>106</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>39000</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>25000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="1">
         <v>91</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="3" t="str">
+      <c r="H7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Not Eligible</v>
       </c>
-      <c r="I7" s="3" t="str">
+      <c r="I7" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Basic Income Group</v>
       </c>
-      <c r="J7" s="3" t="str">
+      <c r="J7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Average Performer</v>
       </c>
-      <c r="K7" s="3" t="str">
+      <c r="K7" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Needs Improvement</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>107</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>52000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>68000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>89</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="3" t="str">
+      <c r="H8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Not Eligible</v>
       </c>
-      <c r="I8" s="3" t="str">
+      <c r="I8" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Medium Income Group</v>
       </c>
-      <c r="J8" s="3" t="str">
+      <c r="J8" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Average Performer</v>
       </c>
-      <c r="K8" s="3" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>108</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
         <v>61000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>88000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="1">
         <v>94</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="3" t="str">
+      <c r="H9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Bonus Eligible</v>
       </c>
-      <c r="I9" s="3" t="str">
+      <c r="I9" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Medium Income Group</v>
       </c>
-      <c r="J9" s="3" t="str">
+      <c r="J9" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Top Performer</v>
       </c>
-      <c r="K9" s="3" t="str">
+      <c r="K9" s="1" t="str">
         <f t="shared" si="3"/>
         <v>Very Good</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="21" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="str">
@@ -1224,69 +2072,69 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
     </row>
     <row r="28" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B28" t="str">
@@ -1295,171 +2143,171 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="1">
         <f>SUMIF(C2:C9,"IT",D2:D9)</f>
         <v>196000</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="1">
         <f>COUNTIF(F2:F9,"&gt;90")</f>
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="1">
         <f>AVERAGEIF(E2:E9,"&gt;75000")</f>
         <v>93250</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B54" t="str">
@@ -1468,63 +2316,63 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B63" t="str">
@@ -1533,54 +2381,2880 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="1">
         <f>COUNTIF(G2:G9,"Excellent")</f>
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A13:H17"/>
+    <mergeCell ref="A21:H26"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A56:G61"/>
     <mergeCell ref="A65:G67"/>
     <mergeCell ref="A30:H32"/>
     <mergeCell ref="A36:G38"/>
     <mergeCell ref="A42:G43"/>
     <mergeCell ref="A47:G52"/>
-    <mergeCell ref="A13:H17"/>
-    <mergeCell ref="A21:H26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DAA12E5-0C8B-4E1A-BDB0-CB53B95CFC26}">
+  <dimension ref="A1:N63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>101</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="5">
+        <v>85</v>
+      </c>
+      <c r="E2" s="5">
+        <v>92</v>
+      </c>
+      <c r="F2" s="5">
+        <v>88</v>
+      </c>
+      <c r="G2" s="5">
+        <v>91</v>
+      </c>
+      <c r="H2" s="5">
+        <v>95</v>
+      </c>
+      <c r="I2" s="5">
+        <f>SUM(D2:G2)</f>
+        <v>356</v>
+      </c>
+      <c r="J2" s="5">
+        <f>(I2/400)*100</f>
+        <v>89</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <f>IF(OR(AND(J2&gt;85,H2&gt;90),G2&gt;95),"Approved","Not Approved")</f>
+        <v>Approved</v>
+      </c>
+      <c r="L2" s="5" t="str">
+        <f>IF(J2&gt;=90,"A+",IF(J2&gt;=75,"A",IF(J2&gt;=60,"B",IF(J2&gt;=40,"C","Fail"))))</f>
+        <v>A</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <f>IF(OR(D2&lt;50,E2&lt;50,F2&lt;50,G2&lt;50),"Needs Improvement","Satisfactory")</f>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <f>IF(AND(AND(D2&gt;85,E2&gt;85,F2&gt;85,G2&gt;85),H2&gt;90),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>102</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="5">
+        <v>72</v>
+      </c>
+      <c r="E3" s="5">
+        <v>65</v>
+      </c>
+      <c r="F3" s="5">
+        <v>70</v>
+      </c>
+      <c r="G3" s="5">
+        <v>68</v>
+      </c>
+      <c r="H3" s="5">
+        <v>89</v>
+      </c>
+      <c r="I3" s="5">
+        <f t="shared" ref="I3:I9" si="0">SUM(D3:G3)</f>
+        <v>275</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" ref="J3:J9" si="1">(I3/400)*100</f>
+        <v>68.75</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <f t="shared" ref="K3:K9" si="2">IF(OR(AND(J3&gt;85,H3&gt;90),G3&gt;95),"Approved","Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <f t="shared" ref="L3:L9" si="3">IF(J3&gt;=90,"A+",IF(J3&gt;=75,"A",IF(J3&gt;=60,"B",IF(J3&gt;=40,"C","Fail"))))</f>
+        <v>B</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <f t="shared" ref="M3:M9" si="4">IF(OR(D3&lt;50,E3&lt;50,F3&lt;50,G3&lt;50),"Needs Improvement","Satisfactory")</f>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <f t="shared" ref="N3:N9" si="5">IF(AND(AND(D3&gt;85,E3&gt;85,F3&gt;85,G3&gt;85),H3&gt;90),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>103</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="5">
+        <v>90</v>
+      </c>
+      <c r="E4" s="5">
+        <v>96</v>
+      </c>
+      <c r="F4" s="5">
+        <v>94</v>
+      </c>
+      <c r="G4" s="5">
+        <v>98</v>
+      </c>
+      <c r="H4" s="5">
+        <v>98</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>378</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="1"/>
+        <v>94.5</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Approved</v>
+      </c>
+      <c r="L4" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+      <c r="M4" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N4" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>104</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="5">
+        <v>60</v>
+      </c>
+      <c r="E5" s="5">
+        <v>58</v>
+      </c>
+      <c r="F5" s="5">
+        <v>62</v>
+      </c>
+      <c r="G5" s="5">
+        <v>55</v>
+      </c>
+      <c r="H5" s="5">
+        <v>80</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" si="0"/>
+        <v>235</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="1"/>
+        <v>58.75</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Approved</v>
+      </c>
+      <c r="L5" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
+      <c r="M5" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N5" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>105</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="5">
+        <v>78</v>
+      </c>
+      <c r="E6" s="5">
+        <v>81</v>
+      </c>
+      <c r="F6" s="5">
+        <v>75</v>
+      </c>
+      <c r="G6" s="5">
+        <v>84</v>
+      </c>
+      <c r="H6" s="5">
+        <v>91</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>318</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>79.5</v>
+      </c>
+      <c r="K6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Approved</v>
+      </c>
+      <c r="L6" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+      <c r="M6" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N6" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>106</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="5">
+        <v>88</v>
+      </c>
+      <c r="E7" s="5">
+        <v>73</v>
+      </c>
+      <c r="F7" s="5">
+        <v>85</v>
+      </c>
+      <c r="G7" s="5">
+        <v>79</v>
+      </c>
+      <c r="H7" s="5">
+        <v>93</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>325</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="1"/>
+        <v>81.25</v>
+      </c>
+      <c r="K7" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Approved</v>
+      </c>
+      <c r="L7" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+      <c r="M7" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N7" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>107</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5">
+        <v>55</v>
+      </c>
+      <c r="E8" s="5">
+        <v>49</v>
+      </c>
+      <c r="F8" s="5">
+        <v>60</v>
+      </c>
+      <c r="G8" s="5">
+        <v>52</v>
+      </c>
+      <c r="H8" s="5">
+        <v>76</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>216</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="K8" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Approved</v>
+      </c>
+      <c r="L8" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
+      <c r="M8" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="N8" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>108</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="5">
+        <v>92</v>
+      </c>
+      <c r="E9" s="5">
+        <v>95</v>
+      </c>
+      <c r="F9" s="5">
+        <v>97</v>
+      </c>
+      <c r="G9" s="5">
+        <v>99</v>
+      </c>
+      <c r="H9" s="5">
+        <v>99</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>383</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="1"/>
+        <v>95.75</v>
+      </c>
+      <c r="K9" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Approved</v>
+      </c>
+      <c r="L9" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+      <c r="M9" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>Satisfactory</v>
+      </c>
+      <c r="N9" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="5">
+        <f>SUM(D2:G2)</f>
+        <v>356</v>
+      </c>
+      <c r="C16" s="5">
+        <f>(I2/400)*100</f>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(OR(AND(J2&gt;85,H2&gt;90),G2&gt;95),"Approved","Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(J2&gt;=90,"A+",IF(J2&gt;=75,"A",IF(J2&gt;=60,"B",IF(J2&gt;=40,"C","Fail"))))</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="5">
+        <f>AVERAGEIF(E2:E9,"&gt;70",E2:E9)</f>
+        <v>87.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="5">
+        <f>SUMIF(C2:C9,"12A",D2:D9)</f>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="str">
+        <f>IF(OR(D2&lt;50,E2&lt;50,F2&lt;50,G2&lt;50),"Needs Improvement","Satisfactory")</f>
+        <v>Satisfactory</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="5">
+        <f>COUNTIF(J2:J9,"&gt;90")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="str">
+        <f>IF(AND(AND(D2&gt;85,E2&gt;85,F2&gt;85,G2&gt;85),H2&gt;90),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A18:J23"/>
+    <mergeCell ref="A57:J61"/>
+    <mergeCell ref="A27:J32"/>
+    <mergeCell ref="A36:J37"/>
+    <mergeCell ref="A41:J42"/>
+    <mergeCell ref="A46:J48"/>
+    <mergeCell ref="A52:J53"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A599805-1245-48FF-BDC3-1085F81756C7}">
+  <dimension ref="A1:J62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>101</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="5">
+        <v>800</v>
+      </c>
+      <c r="E2" s="5">
+        <v>50</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(E2&lt;20,"Restock Immediately","Stock Sufficient")</f>
+        <v>Stock Sufficient</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(OR(AND(E2&lt;30,D2&gt;2000),C2="Electronics"),"Fast Moving","Normal")</f>
+        <v>Fast Moving</v>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(D2&gt;7000,"Premium Product",IF(AND(D2&gt;=2000,D2&lt;=7000),"Standard Product","Budget Product"))</f>
+        <v>Budget Product</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>102</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="5">
+        <v>500</v>
+      </c>
+      <c r="E3" s="5">
+        <v>120</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F9" si="0">IF(E3&lt;20,"Restock Immediately","Stock Sufficient")</f>
+        <v>Stock Sufficient</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G9" si="1">IF(OR(AND(E3&lt;30,D3&gt;2000),C3="Electronics"),"Fast Moving","Normal")</f>
+        <v>Fast Moving</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H9" si="2">IF(D3&gt;7000,"Premium Product",IF(AND(D3&gt;=2000,D3&lt;=7000),"Standard Product","Budget Product"))</f>
+        <v>Budget Product</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>103</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="5">
+        <v>9500</v>
+      </c>
+      <c r="E4" s="5">
+        <v>15</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>Restock Immediately</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fast Moving</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="2"/>
+        <v>Premium Product</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>104</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3500</v>
+      </c>
+      <c r="E5" s="5">
+        <v>25</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>Stock Sufficient</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>Fast Moving</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="2"/>
+        <v>Standard Product</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>105</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="5">
+        <v>7000</v>
+      </c>
+      <c r="E6" s="5">
+        <v>10</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>Restock Immediately</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>Fast Moving</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="2"/>
+        <v>Standard Product</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>106</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="5">
+        <v>650</v>
+      </c>
+      <c r="E7" s="5">
+        <v>80</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>Stock Sufficient</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>Budget Product</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>107</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="5">
+        <v>18</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>Restock Immediately</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>Fast Moving</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>Standard Product</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>108</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="5">
+        <v>120</v>
+      </c>
+      <c r="E9" s="5">
+        <v>200</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>Stock Sufficient</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>Budget Product</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="21" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="16"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="str">
+        <f>VLOOKUP(105,A2:E9,2,FALSE)</f>
+        <v>Desk</v>
+      </c>
+      <c r="C17" s="5">
+        <f>VLOOKUP(102,A2:E10,4,FALSE)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(E2&lt;20,"Restock Immediately","Stock Sufficient")</f>
+        <v>Stock Sufficient</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="5">
+        <f>SUMIF(C2:C9,"Electronics",E2:E9)</f>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="5">
+        <f>COUNTIF(E2:E9,"&gt;50")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="5">
+        <f>AVERAGEIF(D2:D9,"&gt;1000",D2:D9)</f>
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="str">
+        <f>IF(OR(AND(E2&lt;30,D2&gt;2000),C2="Electronics"),"Fast Moving","Normal")</f>
+        <v>Fast Moving</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51">
+        <v>45000</v>
+      </c>
+      <c r="C51">
+        <v>52000</v>
+      </c>
+      <c r="D51">
+        <v>61000</v>
+      </c>
+      <c r="E51">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="5">
+        <f>HLOOKUP("March",A50:E51,2,FALSE)</f>
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="str">
+        <f>IF(D2&gt;7000,"Premium Product",IF(AND(D2&gt;=2000,D2&lt;=7000),"Standard Product","Budget Product"))</f>
+        <v>Budget Product</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A56:J60"/>
+    <mergeCell ref="A39:J44"/>
+    <mergeCell ref="A48:J49"/>
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:J15"/>
+    <mergeCell ref="A19:J21"/>
+    <mergeCell ref="A25:J26"/>
+    <mergeCell ref="A30:J31"/>
+    <mergeCell ref="A35:J35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0E6A5E-182C-445B-A70F-0D5688986447}">
+  <dimension ref="A1:P80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="8">
+        <v>65000</v>
+      </c>
+      <c r="E2" s="8">
+        <v>120000</v>
+      </c>
+      <c r="F2" s="8">
+        <v>76</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="8">
+        <v>6</v>
+      </c>
+      <c r="I2" s="8" t="str">
+        <f>IF(OR(AND(E2&gt;100000,F2&gt;95),AND(C2="IT",H2&gt;7)),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+      <c r="J2" s="8" t="str">
+        <f>IF(OR(AND(D2&gt;70000,G2="Excellent",F2&gt;90),E2&gt;130000),"Promotion Approved","Promotion Rejected")</f>
+        <v>Promotion Rejected</v>
+      </c>
+      <c r="K2" s="8" t="str">
+        <f>IF(OR(AND(H2&gt;5,D2&lt;75000),AND(E2&gt;110000,G2="Excellent")),"Eligible","Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+      <c r="L2" s="8" t="str">
+        <f>IF(OR(AND(F2&lt;90,E2&lt;70000),G2="Average",H2&lt;3),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="M2" s="8" t="str">
+        <f>IF(OR(AND(C2="IT",F2&gt;95,E2&gt;90000),AND(C2="Sales",E2&gt;120000,G2="Excellent")),"Selected","Rejected")</f>
+        <v>Rejected</v>
+      </c>
+      <c r="N2" s="8" t="str">
+        <f>IF(OR(AND(H2&gt;8,F2&gt;95),AND(E2&gt;100000,D2&lt;80000),AND(G2="Excellent",C2="IT")),"Eligible","Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+      <c r="O2" s="8" t="str">
+        <f>IF(OR(AND(F2&lt;90,E2&lt;80000),G2="Average",AND(D2&lt;50000,H2&lt;4)),"Required","Not Required")</f>
+        <v>Not Required</v>
+      </c>
+      <c r="P2" s="8" t="str">
+        <f>IF(OR(AND(E2&gt;100000,F2&gt;95,G2="Excellent"),AND(H2&gt;8,D2&gt;80000)),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8">
+        <v>48000</v>
+      </c>
+      <c r="E3" s="8">
+        <v>45000</v>
+      </c>
+      <c r="F3" s="8">
+        <v>89</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="str">
+        <f t="shared" ref="I3:I9" si="0">IF(OR(AND(E3&gt;100000,F3&gt;95),AND(C3="IT",H3&gt;7)),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+      <c r="J3" s="8" t="str">
+        <f t="shared" ref="J3:J9" si="1">IF(OR(AND(D3&gt;70000,G3="Excellent",F3&gt;90),E3&gt;130000),"Promotion Approved","Promotion Rejected")</f>
+        <v>Promotion Rejected</v>
+      </c>
+      <c r="K3" s="8" t="str">
+        <f t="shared" ref="K3:K9" si="2">IF(OR(AND(H3&gt;5,D3&lt;75000),AND(E3&gt;110000,G3="Excellent")),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+      <c r="L3" s="8" t="str">
+        <f t="shared" ref="L3:L9" si="3">IF(OR(AND(F3&lt;90,E3&lt;70000),G3="Average",H3&lt;3),"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="M3" s="8" t="str">
+        <f t="shared" ref="M3:M9" si="4">IF(OR(AND(C3="IT",F3&gt;95,E3&gt;90000),AND(C3="Sales",E3&gt;120000,G3="Excellent")),"Selected","Rejected")</f>
+        <v>Rejected</v>
+      </c>
+      <c r="N3" s="8" t="str">
+        <f t="shared" ref="N3:N9" si="5">IF(OR(AND(H3&gt;8,F3&gt;95),AND(E3&gt;100000,D3&lt;80000),AND(G3="Excellent",C3="IT")),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+      <c r="O3" s="8" t="str">
+        <f t="shared" ref="O3:O9" si="6">IF(OR(AND(F3&lt;90,E3&lt;80000),G3="Average",AND(D3&lt;50000,H3&lt;4)),"Required","Not Required")</f>
+        <v>Required</v>
+      </c>
+      <c r="P3" s="8" t="str">
+        <f t="shared" ref="P3:P9" si="7">IF(OR(AND(E3&gt;100000,F3&gt;95,G3="Excellent"),AND(H3&gt;8,D3&gt;80000)),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8">
+        <v>72000</v>
+      </c>
+      <c r="E4" s="8">
+        <v>98000</v>
+      </c>
+      <c r="F4" s="8">
+        <v>94</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="8">
+        <v>7</v>
+      </c>
+      <c r="I4" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="J4" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Promotion Approved</v>
+      </c>
+      <c r="K4" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Eligible</v>
+      </c>
+      <c r="L4" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+      <c r="M4" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Rejected</v>
+      </c>
+      <c r="N4" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Eligible</v>
+      </c>
+      <c r="O4" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>Not Required</v>
+      </c>
+      <c r="P4" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="8">
+        <v>55000</v>
+      </c>
+      <c r="E5" s="8">
+        <v>76000</v>
+      </c>
+      <c r="F5" s="8">
+        <v>91</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="8">
+        <v>4</v>
+      </c>
+      <c r="I5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="J5" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Promotion Rejected</v>
+      </c>
+      <c r="K5" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="L5" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+      <c r="M5" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Rejected</v>
+      </c>
+      <c r="N5" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="O5" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>Required</v>
+      </c>
+      <c r="P5" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8">
+        <v>81000</v>
+      </c>
+      <c r="E6" s="8">
+        <v>135000</v>
+      </c>
+      <c r="F6" s="8">
+        <v>98</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="8">
+        <v>9</v>
+      </c>
+      <c r="I6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+      <c r="J6" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Promotion Approved</v>
+      </c>
+      <c r="K6" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Eligible</v>
+      </c>
+      <c r="L6" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+      <c r="M6" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Selected</v>
+      </c>
+      <c r="N6" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Eligible</v>
+      </c>
+      <c r="O6" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>Not Required</v>
+      </c>
+      <c r="P6" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="8">
+        <v>43000</v>
+      </c>
+      <c r="E7" s="8">
+        <v>39000</v>
+      </c>
+      <c r="F7" s="8">
+        <v>93</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="8">
+        <v>5</v>
+      </c>
+      <c r="I7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="J7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Promotion Rejected</v>
+      </c>
+      <c r="K7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="L7" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+      <c r="M7" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Rejected</v>
+      </c>
+      <c r="N7" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="O7" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>Not Required</v>
+      </c>
+      <c r="P7" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="8">
+        <v>59000</v>
+      </c>
+      <c r="E8" s="8">
+        <v>68000</v>
+      </c>
+      <c r="F8" s="8">
+        <v>87</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="8">
+        <v>2</v>
+      </c>
+      <c r="I8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="J8" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Promotion Rejected</v>
+      </c>
+      <c r="K8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="L8" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+      <c r="M8" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Rejected</v>
+      </c>
+      <c r="N8" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="O8" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>Required</v>
+      </c>
+      <c r="P8" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="8">
+        <v>70000</v>
+      </c>
+      <c r="E9" s="8">
+        <v>112000</v>
+      </c>
+      <c r="F9" s="8">
+        <v>97</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="8">
+        <v>8</v>
+      </c>
+      <c r="I9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+      <c r="J9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Promotion Rejected</v>
+      </c>
+      <c r="K9" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>Eligible</v>
+      </c>
+      <c r="L9" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+      <c r="M9" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Selected</v>
+      </c>
+      <c r="N9" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Eligible</v>
+      </c>
+      <c r="O9" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v>Not Required</v>
+      </c>
+      <c r="P9" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="16"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="str">
+        <f>IF(OR(AND(E2&gt;100000,F2&gt;95),AND(C2="IT",H2&gt;7)),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(OR(AND(D2&gt;70000,G2="Excellent",F2&gt;90),E2&gt;130000),"Promotion Approved","Promotion Rejected")</f>
+        <v>Promotion Rejected</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="str">
+        <f>IF(OR(AND(H2&gt;5,D2&lt;75000),AND(E2&gt;110000,G2="Excellent")),"Eligible","Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(OR(AND(F2&lt;90,E2&lt;70000),G2="Average",H2&lt;3),"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="str">
+        <f>IF(OR(AND(C2="IT",F2&gt;95,E2&gt;90000),AND(C2="Sales",E2&gt;120000,G2="Excellent")),"Selected","Rejected")</f>
+        <v>Rejected</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="9"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="str">
+        <f>IF(OR(AND(H2&gt;8,F2&gt;95),AND(E2&gt;100000,D2&lt;80000),AND(G2="Excellent",C2="IT")),"Eligible","Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="15"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="15"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="15"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="str">
+        <f>IF(OR(AND(F2&lt;90,E2&lt;80000),G2="Average",AND(D2&lt;50000,H2&lt;4)),"Required","Not Required")</f>
+        <v>Not Required</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="15"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="15"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="str">
+        <f>IF(OR(AND(E2&gt;100000,F2&gt;95,G2="Excellent"),AND(H2&gt;8,D2&gt;80000)),"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A75:J78"/>
+    <mergeCell ref="A49:J53"/>
+    <mergeCell ref="A57:J62"/>
+    <mergeCell ref="A66:J71"/>
+    <mergeCell ref="A32:J36"/>
+    <mergeCell ref="A41:J45"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:J18"/>
+    <mergeCell ref="A22:J28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
